--- a/results/img_proj_tab/exp4/metrics_predictions_MedViT2_nopt.xlsx
+++ b/results/img_proj_tab/exp4/metrics_predictions_MedViT2_nopt.xlsx
@@ -8,9 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="edca_all_data_predictions_1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="edca_all_features_predictions_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="edca_all_samples_predictions_1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="edca_predictions_1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="edca_selected_image_features_pr" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="edca_all_features_predictions_1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="edca_all_tabular_features_predi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="edca_selected_tabular_features_" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="edca_all_samples_predictions_1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="edca_all_image_features_predict" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="edca_predictions_1" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2068,43 +2072,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.631</v>
+        <v>0.519</v>
       </c>
       <c r="C2" t="n">
-        <v>0.711</v>
+        <v>0.618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.722</v>
+        <v>0.659</v>
       </c>
       <c r="E2" t="n">
-        <v>0.715</v>
+        <v>0.633</v>
       </c>
       <c r="F2" t="n">
-        <v>0.636</v>
+        <v>0.514</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.537</v>
       </c>
       <c r="H2" t="n">
-        <v>0.275</v>
+        <v>0.044</v>
       </c>
       <c r="I2" t="n">
-        <v>0.792</v>
+        <v>0.733</v>
       </c>
       <c r="J2" t="n">
-        <v>0.835</v>
+        <v>0.833</v>
       </c>
       <c r="K2" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L2" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="M2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3">
@@ -2114,43 +2118,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.642</v>
+        <v>0.5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.716</v>
+        <v>0.603</v>
       </c>
       <c r="D3" t="n">
-        <v>0.722</v>
+        <v>0.719</v>
       </c>
       <c r="E3" t="n">
-        <v>0.719</v>
+        <v>0.611</v>
       </c>
       <c r="F3" t="n">
-        <v>0.645</v>
+        <v>0.429</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.29</v>
+        <v>0.002</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.724</v>
       </c>
       <c r="J3" t="n">
-        <v>0.821</v>
+        <v>0.989</v>
       </c>
       <c r="K3" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="M3" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>368</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4">
@@ -2160,43 +2164,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.652</v>
+        <v>0.507</v>
       </c>
       <c r="C4" t="n">
-        <v>0.722</v>
+        <v>0.628</v>
       </c>
       <c r="D4" t="n">
-        <v>0.724</v>
+        <v>0.716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.723</v>
+        <v>0.623</v>
       </c>
       <c r="F4" t="n">
-        <v>0.653</v>
+        <v>0.453</v>
       </c>
       <c r="G4" t="n">
-        <v>0.659</v>
+        <v>0.539</v>
       </c>
       <c r="H4" t="n">
-        <v>0.305</v>
+        <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.727</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.973</v>
       </c>
       <c r="K4" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="M4" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>364</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5">
@@ -2206,43 +2210,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.634</v>
+        <v>0.511</v>
       </c>
       <c r="C5" t="n">
-        <v>0.712</v>
+        <v>0.616</v>
       </c>
       <c r="D5" t="n">
-        <v>0.722</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.717</v>
+        <v>0.632</v>
       </c>
       <c r="F5" t="n">
-        <v>0.639</v>
+        <v>0.487</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="H5" t="n">
-        <v>0.28</v>
+        <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.795</v>
+        <v>0.729</v>
       </c>
       <c r="J5" t="n">
-        <v>0.83</v>
+        <v>0.911</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="M5" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="N5" t="n">
-        <v>372</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6">
@@ -2252,43 +2256,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.633</v>
+        <v>0.482</v>
       </c>
       <c r="C6" t="n">
-        <v>0.712</v>
+        <v>0.578</v>
       </c>
       <c r="D6" t="n">
-        <v>0.722</v>
+        <v>0.656</v>
       </c>
       <c r="E6" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.716</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.794</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.833</v>
+        <v>0.871</v>
       </c>
       <c r="K6" t="n">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="L6" t="n">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="N6" t="n">
-        <v>373</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
@@ -2298,43 +2302,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.633</v>
+        <v>0.5</v>
       </c>
       <c r="C7" t="n">
-        <v>0.713</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.725</v>
+        <v>0.724</v>
       </c>
       <c r="E7" t="n">
-        <v>0.718</v>
+        <v>0.608</v>
       </c>
       <c r="F7" t="n">
-        <v>0.639</v>
+        <v>0.42</v>
       </c>
       <c r="G7" t="n">
-        <v>0.633</v>
+        <v>0.532</v>
       </c>
       <c r="H7" t="n">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.793</v>
+        <v>0.724</v>
       </c>
       <c r="J7" t="n">
-        <v>0.839</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="M7" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>376</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -2344,43 +2348,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.636</v>
+        <v>0.52</v>
       </c>
       <c r="C8" t="n">
-        <v>0.713</v>
+        <v>0.64</v>
       </c>
       <c r="D8" t="n">
-        <v>0.722</v>
+        <v>0.711</v>
       </c>
       <c r="E8" t="n">
-        <v>0.717</v>
+        <v>0.639</v>
       </c>
       <c r="F8" t="n">
-        <v>0.64</v>
+        <v>0.489</v>
       </c>
       <c r="G8" t="n">
-        <v>0.703</v>
+        <v>0.513</v>
       </c>
       <c r="H8" t="n">
-        <v>0.283</v>
+        <v>0.073</v>
       </c>
       <c r="I8" t="n">
-        <v>0.796</v>
+        <v>0.732</v>
       </c>
       <c r="J8" t="n">
-        <v>0.828</v>
+        <v>0.946</v>
       </c>
       <c r="K8" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="M8" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="N8" t="n">
-        <v>371</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -2390,43 +2394,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.63</v>
+        <v>0.513</v>
       </c>
       <c r="C9" t="n">
-        <v>0.706</v>
+        <v>0.636</v>
       </c>
       <c r="D9" t="n">
-        <v>0.712</v>
+        <v>0.714</v>
       </c>
       <c r="E9" t="n">
-        <v>0.709</v>
+        <v>0.631</v>
       </c>
       <c r="F9" t="n">
-        <v>0.632</v>
+        <v>0.47</v>
       </c>
       <c r="G9" t="n">
-        <v>0.673</v>
+        <v>0.532</v>
       </c>
       <c r="H9" t="n">
-        <v>0.265</v>
+        <v>0.057</v>
       </c>
       <c r="I9" t="n">
-        <v>0.793</v>
+        <v>0.729</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.962</v>
       </c>
       <c r="K9" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="L9" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>365</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10">
@@ -2436,43 +2440,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.634</v>
+        <v>0.508</v>
       </c>
       <c r="C10" t="n">
-        <v>0.711</v>
+        <v>0.608</v>
       </c>
       <c r="D10" t="n">
-        <v>0.719</v>
+        <v>0.654</v>
       </c>
       <c r="E10" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="F10" t="n">
-        <v>0.638</v>
+        <v>0.501</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.523</v>
       </c>
       <c r="H10" t="n">
-        <v>0.277</v>
+        <v>0.019</v>
       </c>
       <c r="I10" t="n">
-        <v>0.795</v>
+        <v>0.728</v>
       </c>
       <c r="J10" t="n">
-        <v>0.824</v>
+        <v>0.835</v>
       </c>
       <c r="K10" t="n">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="M10" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N10" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11">
@@ -2482,43 +2486,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.624</v>
+        <v>0.52</v>
       </c>
       <c r="C11" t="n">
-        <v>0.707</v>
+        <v>0.62</v>
       </c>
       <c r="D11" t="n">
-        <v>0.721</v>
+        <v>0.659</v>
       </c>
       <c r="E11" t="n">
-        <v>0.712</v>
+        <v>0.634</v>
       </c>
       <c r="F11" t="n">
-        <v>0.63</v>
+        <v>0.517</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="H11" t="n">
-        <v>0.264</v>
+        <v>0.047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.788</v>
+        <v>0.734</v>
       </c>
       <c r="J11" t="n">
-        <v>0.839</v>
+        <v>0.83</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="M11" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N11" t="n">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12">
@@ -2528,43 +2532,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="C12" t="n">
-        <v>0.708</v>
+        <v>0.8</v>
       </c>
       <c r="D12" t="n">
-        <v>0.716</v>
+        <v>0.724</v>
       </c>
       <c r="E12" t="n">
-        <v>0.711</v>
+        <v>0.608</v>
       </c>
       <c r="F12" t="n">
-        <v>0.634</v>
+        <v>0.42</v>
       </c>
       <c r="G12" t="n">
-        <v>0.659</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.268</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.793</v>
+        <v>0.724</v>
       </c>
       <c r="J12" t="n">
-        <v>0.821</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>96</v>
+        <v>171</v>
       </c>
       <c r="M12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>368</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13">
@@ -2574,43 +2578,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.648</v>
+        <v>0.501</v>
       </c>
       <c r="C13" t="n">
-        <v>0.72</v>
+        <v>0.607</v>
       </c>
       <c r="D13" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.724</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.804</v>
-      </c>
       <c r="J13" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.984</v>
       </c>
       <c r="K13" t="n">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c r="M13" t="n">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="N13" t="n">
-        <v>366</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14">
@@ -2620,43 +2624,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.642</v>
+        <v>0.513</v>
       </c>
       <c r="C14" t="n">
-        <v>0.718</v>
+        <v>0.612</v>
       </c>
       <c r="D14" t="n">
-        <v>0.725</v>
+        <v>0.646</v>
       </c>
       <c r="E14" t="n">
-        <v>0.721</v>
+        <v>0.626</v>
       </c>
       <c r="F14" t="n">
-        <v>0.646</v>
+        <v>0.51</v>
       </c>
       <c r="G14" t="n">
-        <v>0.67</v>
+        <v>0.504</v>
       </c>
       <c r="H14" t="n">
-        <v>0.293</v>
+        <v>0.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="J14" t="n">
-        <v>0.828</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="L14" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="M14" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N14" t="n">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15">
@@ -2666,43 +2670,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.653</v>
+        <v>0.486</v>
       </c>
       <c r="C15" t="n">
-        <v>0.727</v>
+        <v>0.584</v>
       </c>
       <c r="D15" t="n">
-        <v>0.733</v>
+        <v>0.648</v>
       </c>
       <c r="E15" t="n">
-        <v>0.73</v>
+        <v>0.607</v>
       </c>
       <c r="F15" t="n">
-        <v>0.657</v>
+        <v>0.469</v>
       </c>
       <c r="G15" t="n">
-        <v>0.678</v>
+        <v>0.522</v>
       </c>
       <c r="H15" t="n">
-        <v>0.315</v>
+        <v>-0.037</v>
       </c>
       <c r="I15" t="n">
-        <v>0.806</v>
+        <v>0.717</v>
       </c>
       <c r="J15" t="n">
-        <v>0.833</v>
+        <v>0.848</v>
       </c>
       <c r="K15" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="L15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="M15" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="N15" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16">
@@ -2712,43 +2716,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.614</v>
+        <v>0.503</v>
       </c>
       <c r="C16" t="n">
-        <v>0.699</v>
+        <v>0.612</v>
       </c>
       <c r="D16" t="n">
-        <v>0.716</v>
+        <v>0.712</v>
       </c>
       <c r="E16" t="n">
-        <v>0.705</v>
+        <v>0.618</v>
       </c>
       <c r="F16" t="n">
-        <v>0.62</v>
+        <v>0.447</v>
       </c>
       <c r="G16" t="n">
-        <v>0.655</v>
+        <v>0.537</v>
       </c>
       <c r="H16" t="n">
-        <v>0.245</v>
+        <v>0.016</v>
       </c>
       <c r="I16" t="n">
-        <v>0.782</v>
+        <v>0.725</v>
       </c>
       <c r="J16" t="n">
-        <v>0.842</v>
+        <v>0.971</v>
       </c>
       <c r="K16" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="M16" t="n">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="N16" t="n">
-        <v>377</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17">
@@ -2758,43 +2762,43 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.634</v>
+        <v>0.511</v>
       </c>
       <c r="C17" t="n">
-        <v>0.712</v>
+        <v>0.612</v>
       </c>
       <c r="D17" t="n">
-        <v>0.722</v>
+        <v>0.659</v>
       </c>
       <c r="E17" t="n">
-        <v>0.717</v>
+        <v>0.628</v>
       </c>
       <c r="F17" t="n">
-        <v>0.639</v>
+        <v>0.504</v>
       </c>
       <c r="G17" t="n">
-        <v>0.694</v>
+        <v>0.493</v>
       </c>
       <c r="H17" t="n">
-        <v>0.28</v>
+        <v>0.027</v>
       </c>
       <c r="I17" t="n">
-        <v>0.795</v>
+        <v>0.729</v>
       </c>
       <c r="J17" t="n">
-        <v>0.83</v>
+        <v>0.842</v>
       </c>
       <c r="K17" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="L17" t="n">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="M17" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="N17" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18">
@@ -2804,43 +2808,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.635</v>
+        <v>0.5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.714</v>
+        <v>0.603</v>
       </c>
       <c r="D18" t="n">
-        <v>0.725</v>
+        <v>0.719</v>
       </c>
       <c r="E18" t="n">
-        <v>0.719</v>
+        <v>0.611</v>
       </c>
       <c r="F18" t="n">
-        <v>0.64</v>
+        <v>0.429</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.283</v>
+        <v>0.002</v>
       </c>
       <c r="I18" t="n">
-        <v>0.794</v>
+        <v>0.724</v>
       </c>
       <c r="J18" t="n">
-        <v>0.837</v>
+        <v>0.989</v>
       </c>
       <c r="K18" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="M18" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>375</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19">
@@ -2850,43 +2854,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.645</v>
+        <v>0.502</v>
       </c>
       <c r="C19" t="n">
-        <v>0.72</v>
+        <v>0.603</v>
       </c>
       <c r="D19" t="n">
-        <v>0.727</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.723</v>
+        <v>0.622</v>
       </c>
       <c r="F19" t="n">
-        <v>0.649</v>
+        <v>0.469</v>
       </c>
       <c r="G19" t="n">
-        <v>0.658</v>
+        <v>0.521</v>
       </c>
       <c r="H19" t="n">
-        <v>0.299</v>
+        <v>0.006</v>
       </c>
       <c r="I19" t="n">
-        <v>0.801</v>
+        <v>0.725</v>
       </c>
       <c r="J19" t="n">
-        <v>0.828</v>
+        <v>0.922</v>
       </c>
       <c r="K19" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="L19" t="n">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="M19" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="N19" t="n">
-        <v>371</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20">
@@ -2896,43 +2900,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.627</v>
+        <v>0.507</v>
       </c>
       <c r="C20" t="n">
-        <v>0.707</v>
+        <v>0.622</v>
       </c>
       <c r="D20" t="n">
-        <v>0.719</v>
+        <v>0.711</v>
       </c>
       <c r="E20" t="n">
-        <v>0.712</v>
+        <v>0.625</v>
       </c>
       <c r="F20" t="n">
-        <v>0.632</v>
+        <v>0.46</v>
       </c>
       <c r="G20" t="n">
-        <v>0.659</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.267</v>
+        <v>0.033</v>
       </c>
       <c r="I20" t="n">
-        <v>0.79</v>
+        <v>0.727</v>
       </c>
       <c r="J20" t="n">
-        <v>0.833</v>
+        <v>0.962</v>
       </c>
       <c r="K20" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="M20" t="n">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="N20" t="n">
-        <v>373</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21">
@@ -2942,43 +2946,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.626</v>
+        <v>0.481</v>
       </c>
       <c r="C21" t="n">
-        <v>0.706</v>
+        <v>0.577</v>
       </c>
       <c r="D21" t="n">
-        <v>0.716</v>
+        <v>0.651</v>
       </c>
       <c r="E21" t="n">
-        <v>0.71</v>
+        <v>0.603</v>
       </c>
       <c r="F21" t="n">
-        <v>0.631</v>
+        <v>0.459</v>
       </c>
       <c r="G21" t="n">
-        <v>0.664</v>
+        <v>0.479</v>
       </c>
       <c r="H21" t="n">
-        <v>0.263</v>
+        <v>-0.052</v>
       </c>
       <c r="I21" t="n">
-        <v>0.791</v>
+        <v>0.715</v>
       </c>
       <c r="J21" t="n">
-        <v>0.826</v>
+        <v>0.862</v>
       </c>
       <c r="K21" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="L21" t="n">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="M21" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="N21" t="n">
-        <v>370</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22">
@@ -2988,43 +2992,43 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.634</v>
+        <v>0.511</v>
       </c>
       <c r="C22" t="n">
-        <v>0.712</v>
+        <v>0.611</v>
       </c>
       <c r="D22" t="n">
-        <v>0.722</v>
+        <v>0.661</v>
       </c>
       <c r="E22" t="n">
-        <v>0.717</v>
+        <v>0.628</v>
       </c>
       <c r="F22" t="n">
-        <v>0.639</v>
+        <v>0.503</v>
       </c>
       <c r="G22" t="n">
-        <v>0.677</v>
+        <v>0.527</v>
       </c>
       <c r="H22" t="n">
-        <v>0.28</v>
+        <v>0.026</v>
       </c>
       <c r="I22" t="n">
-        <v>0.795</v>
+        <v>0.729</v>
       </c>
       <c r="J22" t="n">
-        <v>0.83</v>
+        <v>0.846</v>
       </c>
       <c r="K22" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="L22" t="n">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="M22" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="N22" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="23">
@@ -3034,43 +3038,43 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.632</v>
+        <v>0.5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.712</v>
+        <v>0.6</v>
       </c>
       <c r="D23" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.724</v>
       </c>
-      <c r="E23" t="n">
-        <v>0.717</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.793</v>
-      </c>
       <c r="J23" t="n">
-        <v>0.837</v>
+        <v>0.871</v>
       </c>
       <c r="K23" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="L23" t="n">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="M23" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="N23" t="n">
-        <v>375</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24">
@@ -3080,43 +3084,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.634</v>
+        <v>0.513</v>
       </c>
       <c r="C24" t="n">
-        <v>0.712</v>
+        <v>0.613</v>
       </c>
       <c r="D24" t="n">
-        <v>0.722</v>
+        <v>0.654</v>
       </c>
       <c r="E24" t="n">
-        <v>0.717</v>
+        <v>0.628</v>
       </c>
       <c r="F24" t="n">
-        <v>0.639</v>
+        <v>0.509</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.497</v>
       </c>
       <c r="H24" t="n">
-        <v>0.28</v>
+        <v>0.031</v>
       </c>
       <c r="I24" t="n">
-        <v>0.795</v>
+        <v>0.73</v>
       </c>
       <c r="J24" t="n">
-        <v>0.83</v>
+        <v>0.828</v>
       </c>
       <c r="K24" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="L24" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="M24" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N24" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25">
@@ -3126,43 +3130,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.629</v>
+        <v>0.498</v>
       </c>
       <c r="C25" t="n">
-        <v>0.708</v>
+        <v>0.598</v>
       </c>
       <c r="D25" t="n">
-        <v>0.717</v>
+        <v>0.658</v>
       </c>
       <c r="E25" t="n">
-        <v>0.712</v>
+        <v>0.618</v>
       </c>
       <c r="F25" t="n">
-        <v>0.633</v>
+        <v>0.484</v>
       </c>
       <c r="G25" t="n">
-        <v>0.664</v>
+        <v>0.516</v>
       </c>
       <c r="H25" t="n">
-        <v>0.269</v>
+        <v>-0.006</v>
       </c>
       <c r="I25" t="n">
-        <v>0.792</v>
+        <v>0.723</v>
       </c>
       <c r="J25" t="n">
-        <v>0.826</v>
+        <v>0.855</v>
       </c>
       <c r="K25" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="M25" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="N25" t="n">
-        <v>370</v>
+        <v>383</v>
       </c>
     </row>
     <row r="26">
@@ -3172,43 +3176,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.628</v>
+        <v>0.493</v>
       </c>
       <c r="C26" t="n">
-        <v>0.707</v>
+        <v>0.592</v>
       </c>
       <c r="D26" t="n">
-        <v>0.717</v>
+        <v>0.664</v>
       </c>
       <c r="E26" t="n">
-        <v>0.711</v>
+        <v>0.615</v>
       </c>
       <c r="F26" t="n">
-        <v>0.632</v>
+        <v>0.472</v>
       </c>
       <c r="G26" t="n">
-        <v>0.66</v>
+        <v>0.504</v>
       </c>
       <c r="H26" t="n">
-        <v>0.266</v>
+        <v>-0.019</v>
       </c>
       <c r="I26" t="n">
-        <v>0.791</v>
+        <v>0.721</v>
       </c>
       <c r="J26" t="n">
-        <v>0.828</v>
+        <v>0.875</v>
       </c>
       <c r="K26" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="L26" t="n">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="M26" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="N26" t="n">
-        <v>371</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27">
@@ -3218,43 +3222,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.646</v>
+        <v>0.526</v>
       </c>
       <c r="C27" t="n">
-        <v>0.72</v>
+        <v>0.625</v>
       </c>
       <c r="D27" t="n">
-        <v>0.725</v>
+        <v>0.662</v>
       </c>
       <c r="E27" t="n">
-        <v>0.722</v>
+        <v>0.639</v>
       </c>
       <c r="F27" t="n">
-        <v>0.649</v>
+        <v>0.524</v>
       </c>
       <c r="G27" t="n">
-        <v>0.648</v>
+        <v>0.515</v>
       </c>
       <c r="H27" t="n">
-        <v>0.298</v>
+        <v>0.061</v>
       </c>
       <c r="I27" t="n">
-        <v>0.802</v>
+        <v>0.737</v>
       </c>
       <c r="J27" t="n">
-        <v>0.824</v>
+        <v>0.83</v>
       </c>
       <c r="K27" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="L27" t="n">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="M27" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N27" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28">
@@ -3264,43 +3268,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.643</v>
+        <v>0.491</v>
       </c>
       <c r="C28" t="n">
-        <v>0.719</v>
+        <v>0.586</v>
       </c>
       <c r="D28" t="n">
-        <v>0.729</v>
+        <v>0.677</v>
       </c>
       <c r="E28" t="n">
-        <v>0.723</v>
+        <v>0.612</v>
       </c>
       <c r="F28" t="n">
-        <v>0.647</v>
+        <v>0.459</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.526</v>
       </c>
       <c r="H28" t="n">
-        <v>0.297</v>
+        <v>-0.028</v>
       </c>
       <c r="I28" t="n">
-        <v>0.799</v>
+        <v>0.72</v>
       </c>
       <c r="J28" t="n">
-        <v>0.835</v>
+        <v>0.906</v>
       </c>
       <c r="K28" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="M28" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N28" t="n">
-        <v>374</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29">
@@ -3310,43 +3314,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.639</v>
+        <v>0.517</v>
       </c>
       <c r="C29" t="n">
-        <v>0.714</v>
+        <v>0.616</v>
       </c>
       <c r="D29" t="n">
-        <v>0.721</v>
+        <v>0.649</v>
       </c>
       <c r="E29" t="n">
-        <v>0.717</v>
+        <v>0.629</v>
       </c>
       <c r="F29" t="n">
-        <v>0.642</v>
+        <v>0.515</v>
       </c>
       <c r="G29" t="n">
-        <v>0.672</v>
+        <v>0.505</v>
       </c>
       <c r="H29" t="n">
-        <v>0.285</v>
+        <v>0.039</v>
       </c>
       <c r="I29" t="n">
-        <v>0.798</v>
+        <v>0.732</v>
       </c>
       <c r="J29" t="n">
-        <v>0.821</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="L29" t="n">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="M29" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N29" t="n">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30">
@@ -3356,43 +3360,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.642</v>
+        <v>0.505</v>
       </c>
       <c r="C30" t="n">
-        <v>0.716</v>
+        <v>0.664</v>
       </c>
       <c r="D30" t="n">
-        <v>0.722</v>
+        <v>0.724</v>
       </c>
       <c r="E30" t="n">
-        <v>0.719</v>
+        <v>0.616</v>
       </c>
       <c r="F30" t="n">
-        <v>0.645</v>
+        <v>0.436</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H30" t="n">
-        <v>0.29</v>
+        <v>0.05</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.726</v>
       </c>
       <c r="J30" t="n">
-        <v>0.821</v>
+        <v>0.993</v>
       </c>
       <c r="K30" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="M30" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>368</v>
+        <v>445</v>
       </c>
     </row>
     <row r="31">
@@ -3402,43 +3406,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.636</v>
+        <v>0.523</v>
       </c>
       <c r="C31" t="n">
-        <v>0.709</v>
+        <v>0.627</v>
       </c>
       <c r="D31" t="n">
-        <v>0.711</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.71</v>
+        <v>0.642</v>
       </c>
       <c r="F31" t="n">
-        <v>0.636</v>
+        <v>0.514</v>
       </c>
       <c r="G31" t="n">
-        <v>0.633</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0.273</v>
+        <v>0.061</v>
       </c>
       <c r="I31" t="n">
-        <v>0.798</v>
+        <v>0.735</v>
       </c>
       <c r="J31" t="n">
-        <v>0.804</v>
+        <v>0.877</v>
       </c>
       <c r="K31" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="L31" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="M31" t="n">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="N31" t="n">
-        <v>360</v>
+        <v>393</v>
       </c>
     </row>
     <row r="32">
@@ -3448,43 +3452,43 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.636</v>
+        <v>0.505</v>
       </c>
       <c r="C32" t="n">
-        <v>0.713</v>
+        <v>0.624</v>
       </c>
       <c r="D32" t="n">
-        <v>0.721</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.716</v>
+        <v>0.622</v>
       </c>
       <c r="F32" t="n">
-        <v>0.64</v>
+        <v>0.475</v>
       </c>
       <c r="G32" t="n">
-        <v>0.671</v>
+        <v>0.527</v>
       </c>
       <c r="H32" t="n">
-        <v>0.281</v>
+        <v>0.017</v>
       </c>
       <c r="I32" t="n">
-        <v>0.796</v>
+        <v>0.726</v>
       </c>
       <c r="J32" t="n">
-        <v>0.828</v>
+        <v>0.901</v>
       </c>
       <c r="K32" t="n">
-        <v>75.833</v>
+        <v>18.767</v>
       </c>
       <c r="L32" t="n">
-        <v>95.167</v>
+        <v>152.233</v>
       </c>
       <c r="M32" t="n">
-        <v>77.233</v>
+        <v>44.3</v>
       </c>
       <c r="N32" t="n">
-        <v>370.767</v>
+        <v>403.7</v>
       </c>
     </row>
     <row r="33">
@@ -3494,43 +3498,43 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006</v>
+        <v>0.05</v>
       </c>
       <c r="D33" t="n">
-        <v>0.005</v>
+        <v>0.029</v>
       </c>
       <c r="E33" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="F33" t="n">
-        <v>0.008</v>
+        <v>0.032</v>
       </c>
       <c r="G33" t="n">
-        <v>0.017</v>
+        <v>0.025</v>
       </c>
       <c r="H33" t="n">
-        <v>0.015</v>
+        <v>0.032</v>
       </c>
       <c r="I33" t="n">
         <v>0.005</v>
       </c>
       <c r="J33" t="n">
-        <v>0.008</v>
+        <v>0.065</v>
       </c>
       <c r="K33" t="n">
-        <v>3.68</v>
+        <v>12.561</v>
       </c>
       <c r="L33" t="n">
-        <v>3.68</v>
+        <v>12.561</v>
       </c>
       <c r="M33" t="n">
-        <v>3.774</v>
+        <v>29.176</v>
       </c>
       <c r="N33" t="n">
-        <v>3.774</v>
+        <v>29.176</v>
       </c>
     </row>
   </sheetData>
@@ -3626,43 +3630,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.638</v>
+        <v>0.631</v>
       </c>
       <c r="C2" t="n">
-        <v>0.716</v>
+        <v>0.711</v>
       </c>
       <c r="D2" t="n">
-        <v>0.727</v>
+        <v>0.722</v>
       </c>
       <c r="E2" t="n">
-        <v>0.721</v>
+        <v>0.715</v>
       </c>
       <c r="F2" t="n">
-        <v>0.643</v>
+        <v>0.636</v>
       </c>
       <c r="G2" t="n">
         <v>0.6889999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.289</v>
+        <v>0.275</v>
       </c>
       <c r="I2" t="n">
-        <v>0.796</v>
+        <v>0.792</v>
       </c>
       <c r="J2" t="n">
-        <v>0.837</v>
+        <v>0.835</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N2" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3">
@@ -3672,43 +3676,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.632</v>
+        <v>0.642</v>
       </c>
       <c r="C3" t="n">
-        <v>0.71</v>
+        <v>0.716</v>
       </c>
       <c r="D3" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="E3" t="n">
-        <v>0.715</v>
+        <v>0.719</v>
       </c>
       <c r="F3" t="n">
-        <v>0.636</v>
+        <v>0.645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.275</v>
+        <v>0.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.83</v>
+        <v>0.821</v>
       </c>
       <c r="K3" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="M3" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N3" t="n">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4">
@@ -3718,43 +3722,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.649</v>
+        <v>0.652</v>
       </c>
       <c r="C4" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="D4" t="n">
-        <v>0.725</v>
+        <v>0.724</v>
       </c>
       <c r="E4" t="n">
         <v>0.723</v>
       </c>
       <c r="F4" t="n">
-        <v>0.651</v>
+        <v>0.653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.674</v>
+        <v>0.659</v>
       </c>
       <c r="H4" t="n">
-        <v>0.303</v>
+        <v>0.305</v>
       </c>
       <c r="I4" t="n">
-        <v>0.805</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.819</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L4" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M4" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N4" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5">
@@ -3764,37 +3768,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.632</v>
+        <v>0.634</v>
       </c>
       <c r="C5" t="n">
-        <v>0.71</v>
+        <v>0.712</v>
       </c>
       <c r="D5" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="E5" t="n">
-        <v>0.715</v>
+        <v>0.717</v>
       </c>
       <c r="F5" t="n">
-        <v>0.636</v>
+        <v>0.639</v>
       </c>
       <c r="G5" t="n">
-        <v>0.671</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.275</v>
+        <v>0.28</v>
       </c>
       <c r="I5" t="n">
-        <v>0.793</v>
+        <v>0.795</v>
       </c>
       <c r="J5" t="n">
         <v>0.83</v>
       </c>
       <c r="K5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L5" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M5" t="n">
         <v>76</v>
@@ -3810,43 +3814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.631</v>
+        <v>0.633</v>
       </c>
       <c r="C6" t="n">
-        <v>0.711</v>
+        <v>0.712</v>
       </c>
       <c r="D6" t="n">
         <v>0.722</v>
       </c>
       <c r="E6" t="n">
-        <v>0.715</v>
+        <v>0.716</v>
       </c>
       <c r="F6" t="n">
-        <v>0.636</v>
+        <v>0.638</v>
       </c>
       <c r="G6" t="n">
-        <v>0.67</v>
+        <v>0.673</v>
       </c>
       <c r="H6" t="n">
-        <v>0.275</v>
+        <v>0.278</v>
       </c>
       <c r="I6" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="J6" t="n">
-        <v>0.835</v>
+        <v>0.833</v>
       </c>
       <c r="K6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L6" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M6" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N6" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7">
@@ -3856,43 +3860,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.636</v>
+        <v>0.633</v>
       </c>
       <c r="C7" t="n">
-        <v>0.714</v>
+        <v>0.713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="E7" t="n">
         <v>0.718</v>
       </c>
       <c r="F7" t="n">
-        <v>0.64</v>
+        <v>0.639</v>
       </c>
       <c r="G7" t="n">
-        <v>0.636</v>
+        <v>0.633</v>
       </c>
       <c r="H7" t="n">
-        <v>0.283</v>
+        <v>0.281</v>
       </c>
       <c r="I7" t="n">
-        <v>0.795</v>
+        <v>0.793</v>
       </c>
       <c r="J7" t="n">
-        <v>0.833</v>
+        <v>0.839</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L7" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M7" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N7" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8">
@@ -3902,43 +3906,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.637</v>
+        <v>0.636</v>
       </c>
       <c r="C8" t="n">
-        <v>0.715</v>
+        <v>0.713</v>
       </c>
       <c r="D8" t="n">
-        <v>0.725</v>
+        <v>0.722</v>
       </c>
       <c r="E8" t="n">
-        <v>0.719</v>
+        <v>0.717</v>
       </c>
       <c r="F8" t="n">
-        <v>0.642</v>
+        <v>0.64</v>
       </c>
       <c r="G8" t="n">
-        <v>0.694</v>
+        <v>0.703</v>
       </c>
       <c r="H8" t="n">
-        <v>0.286</v>
+        <v>0.283</v>
       </c>
       <c r="I8" t="n">
         <v>0.796</v>
       </c>
       <c r="J8" t="n">
-        <v>0.835</v>
+        <v>0.828</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L8" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M8" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -3948,43 +3952,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.639</v>
+        <v>0.63</v>
       </c>
       <c r="C9" t="n">
-        <v>0.717</v>
+        <v>0.706</v>
       </c>
       <c r="D9" t="n">
-        <v>0.729</v>
+        <v>0.712</v>
       </c>
       <c r="E9" t="n">
-        <v>0.722</v>
+        <v>0.709</v>
       </c>
       <c r="F9" t="n">
-        <v>0.645</v>
+        <v>0.632</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="H9" t="n">
-        <v>0.292</v>
+        <v>0.265</v>
       </c>
       <c r="I9" t="n">
-        <v>0.797</v>
+        <v>0.793</v>
       </c>
       <c r="J9" t="n">
-        <v>0.839</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L9" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M9" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="N9" t="n">
-        <v>376</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -3994,43 +3998,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.629</v>
+        <v>0.634</v>
       </c>
       <c r="C10" t="n">
-        <v>0.708</v>
+        <v>0.711</v>
       </c>
       <c r="D10" t="n">
         <v>0.719</v>
       </c>
       <c r="E10" t="n">
-        <v>0.713</v>
+        <v>0.714</v>
       </c>
       <c r="F10" t="n">
-        <v>0.633</v>
+        <v>0.638</v>
       </c>
       <c r="G10" t="n">
-        <v>0.701</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.269</v>
+        <v>0.277</v>
       </c>
       <c r="I10" t="n">
-        <v>0.791</v>
+        <v>0.795</v>
       </c>
       <c r="J10" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="K10" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L10" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M10" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N10" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11">
@@ -4040,43 +4044,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.634</v>
+        <v>0.624</v>
       </c>
       <c r="C11" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.712</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.717</v>
-      </c>
       <c r="F11" t="n">
-        <v>0.639</v>
+        <v>0.63</v>
       </c>
       <c r="G11" t="n">
-        <v>0.679</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.28</v>
+        <v>0.264</v>
       </c>
       <c r="I11" t="n">
-        <v>0.795</v>
+        <v>0.788</v>
       </c>
       <c r="J11" t="n">
-        <v>0.83</v>
+        <v>0.839</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L11" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N11" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12">
@@ -4086,31 +4090,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.637</v>
+        <v>0.63</v>
       </c>
       <c r="C12" t="n">
-        <v>0.715</v>
+        <v>0.708</v>
       </c>
       <c r="D12" t="n">
-        <v>0.725</v>
+        <v>0.716</v>
       </c>
       <c r="E12" t="n">
-        <v>0.719</v>
+        <v>0.711</v>
       </c>
       <c r="F12" t="n">
-        <v>0.642</v>
+        <v>0.634</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.659</v>
       </c>
       <c r="H12" t="n">
-        <v>0.286</v>
+        <v>0.268</v>
       </c>
       <c r="I12" t="n">
-        <v>0.796</v>
+        <v>0.793</v>
       </c>
       <c r="J12" t="n">
-        <v>0.835</v>
+        <v>0.821</v>
       </c>
       <c r="K12" t="n">
         <v>75</v>
@@ -4119,10 +4123,10 @@
         <v>96</v>
       </c>
       <c r="M12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N12" t="n">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13">
@@ -4132,43 +4136,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.639</v>
+        <v>0.648</v>
       </c>
       <c r="C13" t="n">
-        <v>0.716</v>
+        <v>0.72</v>
       </c>
       <c r="D13" t="n">
         <v>0.724</v>
       </c>
       <c r="E13" t="n">
-        <v>0.719</v>
+        <v>0.722</v>
       </c>
       <c r="F13" t="n">
-        <v>0.643</v>
+        <v>0.65</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="H13" t="n">
-        <v>0.288</v>
+        <v>0.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.798</v>
+        <v>0.804</v>
       </c>
       <c r="J13" t="n">
-        <v>0.828</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="L13" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M13" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="N13" t="n">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14">
@@ -4178,43 +4182,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.637</v>
+        <v>0.642</v>
       </c>
       <c r="C14" t="n">
-        <v>0.715</v>
+        <v>0.718</v>
       </c>
       <c r="D14" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="E14" t="n">
-        <v>0.718</v>
+        <v>0.721</v>
       </c>
       <c r="F14" t="n">
-        <v>0.642</v>
+        <v>0.646</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="H14" t="n">
-        <v>0.285</v>
+        <v>0.293</v>
       </c>
       <c r="I14" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.83</v>
+        <v>0.828</v>
       </c>
       <c r="K14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L14" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N14" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15">
@@ -4224,43 +4228,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.634</v>
+        <v>0.653</v>
       </c>
       <c r="C15" t="n">
-        <v>0.712</v>
+        <v>0.727</v>
       </c>
       <c r="D15" t="n">
-        <v>0.722</v>
+        <v>0.733</v>
       </c>
       <c r="E15" t="n">
-        <v>0.717</v>
+        <v>0.73</v>
       </c>
       <c r="F15" t="n">
-        <v>0.639</v>
+        <v>0.657</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.678</v>
       </c>
       <c r="H15" t="n">
-        <v>0.28</v>
+        <v>0.315</v>
       </c>
       <c r="I15" t="n">
-        <v>0.795</v>
+        <v>0.806</v>
       </c>
       <c r="J15" t="n">
-        <v>0.83</v>
+        <v>0.833</v>
       </c>
       <c r="K15" t="n">
+        <v>81</v>
+      </c>
+      <c r="L15" t="n">
+        <v>90</v>
+      </c>
+      <c r="M15" t="n">
         <v>75</v>
       </c>
-      <c r="L15" t="n">
-        <v>96</v>
-      </c>
-      <c r="M15" t="n">
-        <v>76</v>
-      </c>
       <c r="N15" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="16">
@@ -4270,43 +4274,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.63</v>
+        <v>0.614</v>
       </c>
       <c r="C16" t="n">
-        <v>0.709</v>
+        <v>0.699</v>
       </c>
       <c r="D16" t="n">
-        <v>0.719</v>
+        <v>0.716</v>
       </c>
       <c r="E16" t="n">
-        <v>0.713</v>
+        <v>0.705</v>
       </c>
       <c r="F16" t="n">
-        <v>0.635</v>
+        <v>0.62</v>
       </c>
       <c r="G16" t="n">
-        <v>0.673</v>
+        <v>0.655</v>
       </c>
       <c r="H16" t="n">
-        <v>0.272</v>
+        <v>0.245</v>
       </c>
       <c r="I16" t="n">
-        <v>0.793</v>
+        <v>0.782</v>
       </c>
       <c r="J16" t="n">
-        <v>0.828</v>
+        <v>0.842</v>
       </c>
       <c r="K16" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="L16" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="M16" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="N16" t="n">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17">
@@ -4316,7 +4320,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.633</v>
+        <v>0.634</v>
       </c>
       <c r="C17" t="n">
         <v>0.712</v>
@@ -4325,34 +4329,34 @@
         <v>0.722</v>
       </c>
       <c r="E17" t="n">
-        <v>0.716</v>
+        <v>0.717</v>
       </c>
       <c r="F17" t="n">
-        <v>0.638</v>
+        <v>0.639</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.694</v>
       </c>
       <c r="H17" t="n">
-        <v>0.278</v>
+        <v>0.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="J17" t="n">
-        <v>0.833</v>
+        <v>0.83</v>
       </c>
       <c r="K17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L17" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M17" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N17" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18">
@@ -4362,37 +4366,37 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.638</v>
+        <v>0.635</v>
       </c>
       <c r="C18" t="n">
-        <v>0.716</v>
+        <v>0.714</v>
       </c>
       <c r="D18" t="n">
-        <v>0.727</v>
+        <v>0.725</v>
       </c>
       <c r="E18" t="n">
-        <v>0.721</v>
+        <v>0.719</v>
       </c>
       <c r="F18" t="n">
-        <v>0.643</v>
+        <v>0.64</v>
       </c>
       <c r="G18" t="n">
-        <v>0.697</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.289</v>
+        <v>0.283</v>
       </c>
       <c r="I18" t="n">
-        <v>0.796</v>
+        <v>0.794</v>
       </c>
       <c r="J18" t="n">
         <v>0.837</v>
       </c>
       <c r="K18" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L18" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M18" t="n">
         <v>73</v>
@@ -4408,43 +4412,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.63</v>
+        <v>0.645</v>
       </c>
       <c r="C19" t="n">
-        <v>0.706</v>
+        <v>0.72</v>
       </c>
       <c r="D19" t="n">
-        <v>0.712</v>
+        <v>0.727</v>
       </c>
       <c r="E19" t="n">
-        <v>0.709</v>
+        <v>0.723</v>
       </c>
       <c r="F19" t="n">
-        <v>0.632</v>
+        <v>0.649</v>
       </c>
       <c r="G19" t="n">
-        <v>0.654</v>
+        <v>0.658</v>
       </c>
       <c r="H19" t="n">
-        <v>0.265</v>
+        <v>0.299</v>
       </c>
       <c r="I19" t="n">
-        <v>0.793</v>
+        <v>0.801</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.828</v>
       </c>
       <c r="K19" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L19" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M19" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N19" t="n">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20">
@@ -4469,7 +4473,7 @@
         <v>0.632</v>
       </c>
       <c r="G20" t="n">
-        <v>0.678</v>
+        <v>0.659</v>
       </c>
       <c r="H20" t="n">
         <v>0.267</v>
@@ -4500,37 +4504,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.632</v>
+        <v>0.626</v>
       </c>
       <c r="C21" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.71</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.714</v>
-      </c>
       <c r="F21" t="n">
-        <v>0.636</v>
+        <v>0.631</v>
       </c>
       <c r="G21" t="n">
-        <v>0.672</v>
+        <v>0.664</v>
       </c>
       <c r="H21" t="n">
-        <v>0.274</v>
+        <v>0.263</v>
       </c>
       <c r="I21" t="n">
-        <v>0.794</v>
+        <v>0.791</v>
       </c>
       <c r="J21" t="n">
         <v>0.826</v>
       </c>
       <c r="K21" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L21" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M21" t="n">
         <v>78</v>
@@ -4546,43 +4550,43 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.637</v>
+        <v>0.634</v>
       </c>
       <c r="C22" t="n">
-        <v>0.713</v>
+        <v>0.712</v>
       </c>
       <c r="D22" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="E22" t="n">
-        <v>0.716</v>
+        <v>0.717</v>
       </c>
       <c r="F22" t="n">
-        <v>0.641</v>
+        <v>0.639</v>
       </c>
       <c r="G22" t="n">
-        <v>0.668</v>
+        <v>0.677</v>
       </c>
       <c r="H22" t="n">
-        <v>0.282</v>
+        <v>0.28</v>
       </c>
       <c r="I22" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="J22" t="n">
-        <v>0.824</v>
+        <v>0.83</v>
       </c>
       <c r="K22" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L22" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M22" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N22" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23">
@@ -4592,43 +4596,43 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.627</v>
+        <v>0.632</v>
       </c>
       <c r="C23" t="n">
-        <v>0.707</v>
+        <v>0.712</v>
       </c>
       <c r="D23" t="n">
-        <v>0.719</v>
+        <v>0.724</v>
       </c>
       <c r="E23" t="n">
-        <v>0.712</v>
+        <v>0.717</v>
       </c>
       <c r="F23" t="n">
-        <v>0.632</v>
+        <v>0.637</v>
       </c>
       <c r="G23" t="n">
-        <v>0.677</v>
+        <v>0.642</v>
       </c>
       <c r="H23" t="n">
-        <v>0.267</v>
+        <v>0.278</v>
       </c>
       <c r="I23" t="n">
-        <v>0.79</v>
+        <v>0.793</v>
       </c>
       <c r="J23" t="n">
-        <v>0.833</v>
+        <v>0.837</v>
       </c>
       <c r="K23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L23" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M23" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N23" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="24">
@@ -4638,43 +4642,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.629</v>
+        <v>0.634</v>
       </c>
       <c r="C24" t="n">
-        <v>0.71</v>
+        <v>0.712</v>
       </c>
       <c r="D24" t="n">
         <v>0.722</v>
       </c>
       <c r="E24" t="n">
-        <v>0.715</v>
+        <v>0.717</v>
       </c>
       <c r="F24" t="n">
-        <v>0.635</v>
+        <v>0.639</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.272</v>
+        <v>0.28</v>
       </c>
       <c r="I24" t="n">
-        <v>0.791</v>
+        <v>0.795</v>
       </c>
       <c r="J24" t="n">
-        <v>0.837</v>
+        <v>0.83</v>
       </c>
       <c r="K24" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L24" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M24" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N24" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25">
@@ -4684,43 +4688,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.627</v>
+        <v>0.629</v>
       </c>
       <c r="C25" t="n">
-        <v>0.707</v>
+        <v>0.708</v>
       </c>
       <c r="D25" t="n">
-        <v>0.719</v>
+        <v>0.717</v>
       </c>
       <c r="E25" t="n">
         <v>0.712</v>
       </c>
       <c r="F25" t="n">
-        <v>0.632</v>
+        <v>0.633</v>
       </c>
       <c r="G25" t="n">
-        <v>0.662</v>
+        <v>0.664</v>
       </c>
       <c r="H25" t="n">
-        <v>0.267</v>
+        <v>0.269</v>
       </c>
       <c r="I25" t="n">
-        <v>0.79</v>
+        <v>0.792</v>
       </c>
       <c r="J25" t="n">
-        <v>0.833</v>
+        <v>0.826</v>
       </c>
       <c r="K25" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L25" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M25" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N25" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26">
@@ -4730,43 +4734,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.64</v>
+        <v>0.628</v>
       </c>
       <c r="C26" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D26" t="n">
         <v>0.717</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.727</v>
-      </c>
       <c r="E26" t="n">
-        <v>0.721</v>
+        <v>0.711</v>
       </c>
       <c r="F26" t="n">
-        <v>0.645</v>
+        <v>0.632</v>
       </c>
       <c r="G26" t="n">
-        <v>0.661</v>
+        <v>0.66</v>
       </c>
       <c r="H26" t="n">
-        <v>0.291</v>
+        <v>0.266</v>
       </c>
       <c r="I26" t="n">
-        <v>0.797</v>
+        <v>0.791</v>
       </c>
       <c r="J26" t="n">
-        <v>0.835</v>
+        <v>0.828</v>
       </c>
       <c r="K26" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L26" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M26" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N26" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27">
@@ -4776,43 +4780,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.634</v>
+        <v>0.646</v>
       </c>
       <c r="C27" t="n">
-        <v>0.712</v>
+        <v>0.72</v>
       </c>
       <c r="D27" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.722</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.717</v>
-      </c>
       <c r="F27" t="n">
-        <v>0.639</v>
+        <v>0.649</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.648</v>
       </c>
       <c r="H27" t="n">
-        <v>0.28</v>
+        <v>0.298</v>
       </c>
       <c r="I27" t="n">
-        <v>0.795</v>
+        <v>0.802</v>
       </c>
       <c r="J27" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="K27" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L27" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="M27" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N27" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28">
@@ -4822,43 +4826,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.639</v>
+        <v>0.643</v>
       </c>
       <c r="C28" t="n">
-        <v>0.716</v>
+        <v>0.719</v>
       </c>
       <c r="D28" t="n">
-        <v>0.725</v>
+        <v>0.729</v>
       </c>
       <c r="E28" t="n">
-        <v>0.72</v>
+        <v>0.723</v>
       </c>
       <c r="F28" t="n">
-        <v>0.643</v>
+        <v>0.647</v>
       </c>
       <c r="G28" t="n">
         <v>0.6840000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.288</v>
+        <v>0.297</v>
       </c>
       <c r="I28" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="J28" t="n">
-        <v>0.833</v>
+        <v>0.835</v>
       </c>
       <c r="K28" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L28" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M28" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N28" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="29">
@@ -4868,43 +4872,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.634</v>
+        <v>0.639</v>
       </c>
       <c r="C29" t="n">
-        <v>0.712</v>
+        <v>0.714</v>
       </c>
       <c r="D29" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="E29" t="n">
         <v>0.717</v>
       </c>
       <c r="F29" t="n">
-        <v>0.639</v>
+        <v>0.642</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="H29" t="n">
-        <v>0.28</v>
+        <v>0.285</v>
       </c>
       <c r="I29" t="n">
-        <v>0.795</v>
+        <v>0.798</v>
       </c>
       <c r="J29" t="n">
-        <v>0.83</v>
+        <v>0.821</v>
       </c>
       <c r="K29" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L29" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M29" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N29" t="n">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="30">
@@ -4914,43 +4918,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.641</v>
+        <v>0.642</v>
       </c>
       <c r="C30" t="n">
         <v>0.716</v>
       </c>
       <c r="D30" t="n">
-        <v>0.724</v>
+        <v>0.722</v>
       </c>
       <c r="E30" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="F30" t="n">
         <v>0.645</v>
       </c>
       <c r="G30" t="n">
-        <v>0.678</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>0.29</v>
       </c>
       <c r="I30" t="n">
-        <v>0.799</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0.826</v>
+        <v>0.821</v>
       </c>
       <c r="K30" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L30" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M30" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N30" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="31">
@@ -4960,31 +4964,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.639</v>
+        <v>0.636</v>
       </c>
       <c r="C31" t="n">
-        <v>0.713</v>
+        <v>0.709</v>
       </c>
       <c r="D31" t="n">
-        <v>0.716</v>
+        <v>0.711</v>
       </c>
       <c r="E31" t="n">
-        <v>0.714</v>
+        <v>0.71</v>
       </c>
       <c r="F31" t="n">
-        <v>0.641</v>
+        <v>0.636</v>
       </c>
       <c r="G31" t="n">
-        <v>0.638</v>
+        <v>0.633</v>
       </c>
       <c r="H31" t="n">
-        <v>0.281</v>
+        <v>0.273</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.798</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.804</v>
       </c>
       <c r="K31" t="n">
         <v>80</v>
@@ -4993,10 +4997,10 @@
         <v>91</v>
       </c>
       <c r="M31" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N31" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="32">
@@ -5006,43 +5010,43 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.635</v>
+        <v>0.636</v>
       </c>
       <c r="C32" t="n">
         <v>0.713</v>
       </c>
       <c r="D32" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="E32" t="n">
-        <v>0.717</v>
+        <v>0.716</v>
       </c>
       <c r="F32" t="n">
-        <v>0.639</v>
+        <v>0.64</v>
       </c>
       <c r="G32" t="n">
-        <v>0.678</v>
+        <v>0.671</v>
       </c>
       <c r="H32" t="n">
-        <v>0.28</v>
+        <v>0.281</v>
       </c>
       <c r="I32" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="J32" t="n">
-        <v>0.83</v>
+        <v>0.828</v>
       </c>
       <c r="K32" t="n">
-        <v>75.09999999999999</v>
+        <v>75.833</v>
       </c>
       <c r="L32" t="n">
-        <v>95.90000000000001</v>
+        <v>95.167</v>
       </c>
       <c r="M32" t="n">
-        <v>76.09999999999999</v>
+        <v>77.233</v>
       </c>
       <c r="N32" t="n">
-        <v>371.9</v>
+        <v>370.767</v>
       </c>
     </row>
     <row r="33">
@@ -5052,43 +5056,43 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="D33" t="n">
         <v>0.005</v>
       </c>
-      <c r="C33" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.004</v>
-      </c>
       <c r="E33" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="F33" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I33" t="n">
         <v>0.005</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.003</v>
-      </c>
       <c r="J33" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="K33" t="n">
-        <v>2.181</v>
+        <v>3.68</v>
       </c>
       <c r="L33" t="n">
-        <v>2.181</v>
+        <v>3.68</v>
       </c>
       <c r="M33" t="n">
-        <v>2.821</v>
+        <v>3.774</v>
       </c>
       <c r="N33" t="n">
-        <v>2.821</v>
+        <v>3.774</v>
       </c>
     </row>
   </sheetData>
@@ -5184,6 +5188,6238 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K2" t="n">
+        <v>74</v>
+      </c>
+      <c r="L2" t="n">
+        <v>97</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:08:15.888227</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K3" t="n">
+        <v>74</v>
+      </c>
+      <c r="L3" t="n">
+        <v>97</v>
+      </c>
+      <c r="M3" t="n">
+        <v>73</v>
+      </c>
+      <c r="N3" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:31:46.968463</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="K4" t="n">
+        <v>79</v>
+      </c>
+      <c r="L4" t="n">
+        <v>92</v>
+      </c>
+      <c r="M4" t="n">
+        <v>84</v>
+      </c>
+      <c r="N4" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:48:38.803271</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K5" t="n">
+        <v>76</v>
+      </c>
+      <c r="L5" t="n">
+        <v>95</v>
+      </c>
+      <c r="M5" t="n">
+        <v>75</v>
+      </c>
+      <c r="N5" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 09:59:36.444055</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>94</v>
+      </c>
+      <c r="M6" t="n">
+        <v>75</v>
+      </c>
+      <c r="N6" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 10:29:05.050771</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K7" t="n">
+        <v>73</v>
+      </c>
+      <c r="L7" t="n">
+        <v>98</v>
+      </c>
+      <c r="M7" t="n">
+        <v>73</v>
+      </c>
+      <c r="N7" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 10:55:14.122679</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K8" t="n">
+        <v>74</v>
+      </c>
+      <c r="L8" t="n">
+        <v>97</v>
+      </c>
+      <c r="M8" t="n">
+        <v>75</v>
+      </c>
+      <c r="N8" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 11:34:23.542862</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K9" t="n">
+        <v>74</v>
+      </c>
+      <c r="L9" t="n">
+        <v>97</v>
+      </c>
+      <c r="M9" t="n">
+        <v>74</v>
+      </c>
+      <c r="N9" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 12:06:43.200045</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K10" t="n">
+        <v>74</v>
+      </c>
+      <c r="L10" t="n">
+        <v>97</v>
+      </c>
+      <c r="M10" t="n">
+        <v>78</v>
+      </c>
+      <c r="N10" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 12:35:25.531310</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K11" t="n">
+        <v>75</v>
+      </c>
+      <c r="L11" t="n">
+        <v>96</v>
+      </c>
+      <c r="M11" t="n">
+        <v>79</v>
+      </c>
+      <c r="N11" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 13:11:05.045341</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K12" t="n">
+        <v>74</v>
+      </c>
+      <c r="L12" t="n">
+        <v>97</v>
+      </c>
+      <c r="M12" t="n">
+        <v>74</v>
+      </c>
+      <c r="N12" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 13:40:11.319989</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K13" t="n">
+        <v>74</v>
+      </c>
+      <c r="L13" t="n">
+        <v>97</v>
+      </c>
+      <c r="M13" t="n">
+        <v>73</v>
+      </c>
+      <c r="N13" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 14:26:02.720244</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K14" t="n">
+        <v>75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>96</v>
+      </c>
+      <c r="M14" t="n">
+        <v>78</v>
+      </c>
+      <c r="N14" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 15:35:23.127910</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K15" t="n">
+        <v>74</v>
+      </c>
+      <c r="L15" t="n">
+        <v>97</v>
+      </c>
+      <c r="M15" t="n">
+        <v>77</v>
+      </c>
+      <c r="N15" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 16:24:10.880024</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K16" t="n">
+        <v>75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>96</v>
+      </c>
+      <c r="M16" t="n">
+        <v>78</v>
+      </c>
+      <c r="N16" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 17:06:37.273930</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K17" t="n">
+        <v>76</v>
+      </c>
+      <c r="L17" t="n">
+        <v>95</v>
+      </c>
+      <c r="M17" t="n">
+        <v>77</v>
+      </c>
+      <c r="N17" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 18:22:09.060886</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="K18" t="n">
+        <v>76</v>
+      </c>
+      <c r="L18" t="n">
+        <v>95</v>
+      </c>
+      <c r="M18" t="n">
+        <v>72</v>
+      </c>
+      <c r="N18" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 18:50:48.524789</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>76</v>
+      </c>
+      <c r="L19" t="n">
+        <v>95</v>
+      </c>
+      <c r="M19" t="n">
+        <v>82</v>
+      </c>
+      <c r="N19" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 19:30:33.229860</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K20" t="n">
+        <v>75</v>
+      </c>
+      <c r="L20" t="n">
+        <v>96</v>
+      </c>
+      <c r="M20" t="n">
+        <v>74</v>
+      </c>
+      <c r="N20" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 20:32:46.246451</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K21" t="n">
+        <v>74</v>
+      </c>
+      <c r="L21" t="n">
+        <v>97</v>
+      </c>
+      <c r="M21" t="n">
+        <v>77</v>
+      </c>
+      <c r="N21" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 21:42:09.219002</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K22" t="n">
+        <v>76</v>
+      </c>
+      <c r="L22" t="n">
+        <v>95</v>
+      </c>
+      <c r="M22" t="n">
+        <v>78</v>
+      </c>
+      <c r="N22" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 22:46:14.791499</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K23" t="n">
+        <v>79</v>
+      </c>
+      <c r="L23" t="n">
+        <v>92</v>
+      </c>
+      <c r="M23" t="n">
+        <v>79</v>
+      </c>
+      <c r="N23" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 23:52:33.342029</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K24" t="n">
+        <v>74</v>
+      </c>
+      <c r="L24" t="n">
+        <v>97</v>
+      </c>
+      <c r="M24" t="n">
+        <v>78</v>
+      </c>
+      <c r="N24" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 01:07:20.126756</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K25" t="n">
+        <v>74</v>
+      </c>
+      <c r="L25" t="n">
+        <v>97</v>
+      </c>
+      <c r="M25" t="n">
+        <v>77</v>
+      </c>
+      <c r="N25" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 01:44:26.049608</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K26" t="n">
+        <v>77</v>
+      </c>
+      <c r="L26" t="n">
+        <v>94</v>
+      </c>
+      <c r="M26" t="n">
+        <v>78</v>
+      </c>
+      <c r="N26" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 02:23:11.293155</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K27" t="n">
+        <v>74</v>
+      </c>
+      <c r="L27" t="n">
+        <v>97</v>
+      </c>
+      <c r="M27" t="n">
+        <v>78</v>
+      </c>
+      <c r="N27" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 03:12:08.756859</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K28" t="n">
+        <v>77</v>
+      </c>
+      <c r="L28" t="n">
+        <v>94</v>
+      </c>
+      <c r="M28" t="n">
+        <v>74</v>
+      </c>
+      <c r="N28" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 04:22:55.149919</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K29" t="n">
+        <v>76</v>
+      </c>
+      <c r="L29" t="n">
+        <v>95</v>
+      </c>
+      <c r="M29" t="n">
+        <v>78</v>
+      </c>
+      <c r="N29" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 05:06:19.695722</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K30" t="n">
+        <v>74</v>
+      </c>
+      <c r="L30" t="n">
+        <v>97</v>
+      </c>
+      <c r="M30" t="n">
+        <v>73</v>
+      </c>
+      <c r="N30" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 05:31:12.430920</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="K31" t="n">
+        <v>79</v>
+      </c>
+      <c r="L31" t="n">
+        <v>92</v>
+      </c>
+      <c r="M31" t="n">
+        <v>89</v>
+      </c>
+      <c r="N31" t="n">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K32" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>76.93300000000001</v>
+      </c>
+      <c r="N32" t="n">
+        <v>371.067</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.521</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.521</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>balanced_accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>matthews</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tnr</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 07:44:35.868239</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K2" t="n">
+        <v>75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>96</v>
+      </c>
+      <c r="M2" t="n">
+        <v>73</v>
+      </c>
+      <c r="N2" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:08:15.888227</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K3" t="n">
+        <v>74</v>
+      </c>
+      <c r="L3" t="n">
+        <v>97</v>
+      </c>
+      <c r="M3" t="n">
+        <v>73</v>
+      </c>
+      <c r="N3" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:31:46.968463</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="K4" t="n">
+        <v>79</v>
+      </c>
+      <c r="L4" t="n">
+        <v>92</v>
+      </c>
+      <c r="M4" t="n">
+        <v>84</v>
+      </c>
+      <c r="N4" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:48:38.803271</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K5" t="n">
+        <v>75</v>
+      </c>
+      <c r="L5" t="n">
+        <v>96</v>
+      </c>
+      <c r="M5" t="n">
+        <v>76</v>
+      </c>
+      <c r="N5" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 09:59:36.444055</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K6" t="n">
+        <v>76</v>
+      </c>
+      <c r="L6" t="n">
+        <v>95</v>
+      </c>
+      <c r="M6" t="n">
+        <v>76</v>
+      </c>
+      <c r="N6" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 10:29:05.050771</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K7" t="n">
+        <v>79</v>
+      </c>
+      <c r="L7" t="n">
+        <v>92</v>
+      </c>
+      <c r="M7" t="n">
+        <v>79</v>
+      </c>
+      <c r="N7" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 10:55:14.122679</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K8" t="n">
+        <v>74</v>
+      </c>
+      <c r="L8" t="n">
+        <v>97</v>
+      </c>
+      <c r="M8" t="n">
+        <v>75</v>
+      </c>
+      <c r="N8" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 11:34:23.542862</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K9" t="n">
+        <v>74</v>
+      </c>
+      <c r="L9" t="n">
+        <v>97</v>
+      </c>
+      <c r="M9" t="n">
+        <v>73</v>
+      </c>
+      <c r="N9" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 12:06:43.200045</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K10" t="n">
+        <v>75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>96</v>
+      </c>
+      <c r="M10" t="n">
+        <v>77</v>
+      </c>
+      <c r="N10" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 12:35:25.531310</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K11" t="n">
+        <v>75</v>
+      </c>
+      <c r="L11" t="n">
+        <v>96</v>
+      </c>
+      <c r="M11" t="n">
+        <v>79</v>
+      </c>
+      <c r="N11" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 13:11:05.045341</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K12" t="n">
+        <v>75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>96</v>
+      </c>
+      <c r="M12" t="n">
+        <v>74</v>
+      </c>
+      <c r="N12" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 13:40:11.319989</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="K13" t="n">
+        <v>79</v>
+      </c>
+      <c r="L13" t="n">
+        <v>92</v>
+      </c>
+      <c r="M13" t="n">
+        <v>72</v>
+      </c>
+      <c r="N13" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 14:26:02.720244</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K14" t="n">
+        <v>75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>96</v>
+      </c>
+      <c r="M14" t="n">
+        <v>78</v>
+      </c>
+      <c r="N14" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 15:35:23.127910</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K15" t="n">
+        <v>79</v>
+      </c>
+      <c r="L15" t="n">
+        <v>92</v>
+      </c>
+      <c r="M15" t="n">
+        <v>76</v>
+      </c>
+      <c r="N15" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 16:24:10.880024</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K16" t="n">
+        <v>75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>96</v>
+      </c>
+      <c r="M16" t="n">
+        <v>78</v>
+      </c>
+      <c r="N16" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 17:06:37.273930</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K17" t="n">
+        <v>76</v>
+      </c>
+      <c r="L17" t="n">
+        <v>95</v>
+      </c>
+      <c r="M17" t="n">
+        <v>77</v>
+      </c>
+      <c r="N17" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 18:22:09.060886</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K18" t="n">
+        <v>76</v>
+      </c>
+      <c r="L18" t="n">
+        <v>95</v>
+      </c>
+      <c r="M18" t="n">
+        <v>73</v>
+      </c>
+      <c r="N18" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 18:50:48.524789</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>76</v>
+      </c>
+      <c r="L19" t="n">
+        <v>95</v>
+      </c>
+      <c r="M19" t="n">
+        <v>82</v>
+      </c>
+      <c r="N19" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 19:30:33.229860</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K20" t="n">
+        <v>74</v>
+      </c>
+      <c r="L20" t="n">
+        <v>97</v>
+      </c>
+      <c r="M20" t="n">
+        <v>75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 20:32:46.246451</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K21" t="n">
+        <v>74</v>
+      </c>
+      <c r="L21" t="n">
+        <v>97</v>
+      </c>
+      <c r="M21" t="n">
+        <v>77</v>
+      </c>
+      <c r="N21" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 21:42:09.219002</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K22" t="n">
+        <v>73</v>
+      </c>
+      <c r="L22" t="n">
+        <v>98</v>
+      </c>
+      <c r="M22" t="n">
+        <v>76</v>
+      </c>
+      <c r="N22" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 22:46:14.791499</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K23" t="n">
+        <v>73</v>
+      </c>
+      <c r="L23" t="n">
+        <v>98</v>
+      </c>
+      <c r="M23" t="n">
+        <v>75</v>
+      </c>
+      <c r="N23" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 23:52:33.342029</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="K24" t="n">
+        <v>75</v>
+      </c>
+      <c r="L24" t="n">
+        <v>96</v>
+      </c>
+      <c r="M24" t="n">
+        <v>72</v>
+      </c>
+      <c r="N24" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 01:07:20.126756</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K25" t="n">
+        <v>73</v>
+      </c>
+      <c r="L25" t="n">
+        <v>98</v>
+      </c>
+      <c r="M25" t="n">
+        <v>74</v>
+      </c>
+      <c r="N25" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 01:44:26.049608</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K26" t="n">
+        <v>77</v>
+      </c>
+      <c r="L26" t="n">
+        <v>94</v>
+      </c>
+      <c r="M26" t="n">
+        <v>76</v>
+      </c>
+      <c r="N26" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 02:23:11.293155</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K27" t="n">
+        <v>74</v>
+      </c>
+      <c r="L27" t="n">
+        <v>97</v>
+      </c>
+      <c r="M27" t="n">
+        <v>78</v>
+      </c>
+      <c r="N27" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 03:12:08.756859</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K28" t="n">
+        <v>77</v>
+      </c>
+      <c r="L28" t="n">
+        <v>94</v>
+      </c>
+      <c r="M28" t="n">
+        <v>74</v>
+      </c>
+      <c r="N28" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 04:22:55.149919</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K29" t="n">
+        <v>76</v>
+      </c>
+      <c r="L29" t="n">
+        <v>95</v>
+      </c>
+      <c r="M29" t="n">
+        <v>78</v>
+      </c>
+      <c r="N29" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 05:06:19.695722</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K30" t="n">
+        <v>74</v>
+      </c>
+      <c r="L30" t="n">
+        <v>97</v>
+      </c>
+      <c r="M30" t="n">
+        <v>73</v>
+      </c>
+      <c r="N30" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 05:31:12.430920</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="K31" t="n">
+        <v>79</v>
+      </c>
+      <c r="L31" t="n">
+        <v>92</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87</v>
+      </c>
+      <c r="N31" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K32" t="n">
+        <v>75.533</v>
+      </c>
+      <c r="L32" t="n">
+        <v>95.467</v>
+      </c>
+      <c r="M32" t="n">
+        <v>76.333</v>
+      </c>
+      <c r="N32" t="n">
+        <v>371.667</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.399</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>balanced_accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>matthews</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tnr</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 07:44:35.868239</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K2" t="n">
+        <v>75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>96</v>
+      </c>
+      <c r="M2" t="n">
+        <v>73</v>
+      </c>
+      <c r="N2" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:08:15.888227</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K3" t="n">
+        <v>74</v>
+      </c>
+      <c r="L3" t="n">
+        <v>97</v>
+      </c>
+      <c r="M3" t="n">
+        <v>76</v>
+      </c>
+      <c r="N3" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:31:46.968463</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K4" t="n">
+        <v>82</v>
+      </c>
+      <c r="L4" t="n">
+        <v>89</v>
+      </c>
+      <c r="M4" t="n">
+        <v>81</v>
+      </c>
+      <c r="N4" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:48:38.803271</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K5" t="n">
+        <v>74</v>
+      </c>
+      <c r="L5" t="n">
+        <v>97</v>
+      </c>
+      <c r="M5" t="n">
+        <v>76</v>
+      </c>
+      <c r="N5" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 09:59:36.444055</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K6" t="n">
+        <v>73</v>
+      </c>
+      <c r="L6" t="n">
+        <v>98</v>
+      </c>
+      <c r="M6" t="n">
+        <v>74</v>
+      </c>
+      <c r="N6" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 10:29:05.050771</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K7" t="n">
+        <v>75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>96</v>
+      </c>
+      <c r="M7" t="n">
+        <v>75</v>
+      </c>
+      <c r="N7" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 10:55:14.122679</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K8" t="n">
+        <v>75</v>
+      </c>
+      <c r="L8" t="n">
+        <v>96</v>
+      </c>
+      <c r="M8" t="n">
+        <v>74</v>
+      </c>
+      <c r="N8" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 11:34:23.542862</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="K9" t="n">
+        <v>75</v>
+      </c>
+      <c r="L9" t="n">
+        <v>96</v>
+      </c>
+      <c r="M9" t="n">
+        <v>72</v>
+      </c>
+      <c r="N9" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 12:06:43.200045</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K10" t="n">
+        <v>73</v>
+      </c>
+      <c r="L10" t="n">
+        <v>98</v>
+      </c>
+      <c r="M10" t="n">
+        <v>76</v>
+      </c>
+      <c r="N10" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 12:35:25.531310</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K11" t="n">
+        <v>75</v>
+      </c>
+      <c r="L11" t="n">
+        <v>96</v>
+      </c>
+      <c r="M11" t="n">
+        <v>76</v>
+      </c>
+      <c r="N11" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 13:11:05.045341</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K12" t="n">
+        <v>75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>96</v>
+      </c>
+      <c r="M12" t="n">
+        <v>74</v>
+      </c>
+      <c r="N12" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 13:40:11.319989</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>94</v>
+      </c>
+      <c r="M13" t="n">
+        <v>77</v>
+      </c>
+      <c r="N13" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 14:26:02.720244</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K14" t="n">
+        <v>76</v>
+      </c>
+      <c r="L14" t="n">
+        <v>95</v>
+      </c>
+      <c r="M14" t="n">
+        <v>76</v>
+      </c>
+      <c r="N14" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 15:35:23.127910</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K15" t="n">
+        <v>75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>96</v>
+      </c>
+      <c r="M15" t="n">
+        <v>76</v>
+      </c>
+      <c r="N15" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 16:24:10.880024</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K16" t="n">
+        <v>74</v>
+      </c>
+      <c r="L16" t="n">
+        <v>97</v>
+      </c>
+      <c r="M16" t="n">
+        <v>77</v>
+      </c>
+      <c r="N16" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 17:06:37.273930</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K17" t="n">
+        <v>74</v>
+      </c>
+      <c r="L17" t="n">
+        <v>97</v>
+      </c>
+      <c r="M17" t="n">
+        <v>75</v>
+      </c>
+      <c r="N17" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 18:22:09.060886</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K18" t="n">
+        <v>75</v>
+      </c>
+      <c r="L18" t="n">
+        <v>96</v>
+      </c>
+      <c r="M18" t="n">
+        <v>73</v>
+      </c>
+      <c r="N18" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 18:50:48.524789</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>76</v>
+      </c>
+      <c r="L19" t="n">
+        <v>95</v>
+      </c>
+      <c r="M19" t="n">
+        <v>83</v>
+      </c>
+      <c r="N19" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 19:30:33.229860</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K20" t="n">
+        <v>72</v>
+      </c>
+      <c r="L20" t="n">
+        <v>99</v>
+      </c>
+      <c r="M20" t="n">
+        <v>75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 20:32:46.246451</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K21" t="n">
+        <v>75</v>
+      </c>
+      <c r="L21" t="n">
+        <v>96</v>
+      </c>
+      <c r="M21" t="n">
+        <v>78</v>
+      </c>
+      <c r="N21" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 21:42:09.219002</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K22" t="n">
+        <v>77</v>
+      </c>
+      <c r="L22" t="n">
+        <v>94</v>
+      </c>
+      <c r="M22" t="n">
+        <v>79</v>
+      </c>
+      <c r="N22" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 22:46:14.791499</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K23" t="n">
+        <v>72</v>
+      </c>
+      <c r="L23" t="n">
+        <v>99</v>
+      </c>
+      <c r="M23" t="n">
+        <v>75</v>
+      </c>
+      <c r="N23" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 23:52:33.342029</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K24" t="n">
+        <v>72</v>
+      </c>
+      <c r="L24" t="n">
+        <v>99</v>
+      </c>
+      <c r="M24" t="n">
+        <v>73</v>
+      </c>
+      <c r="N24" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 01:07:20.126756</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K25" t="n">
+        <v>72</v>
+      </c>
+      <c r="L25" t="n">
+        <v>99</v>
+      </c>
+      <c r="M25" t="n">
+        <v>75</v>
+      </c>
+      <c r="N25" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 01:44:26.049608</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K26" t="n">
+        <v>76</v>
+      </c>
+      <c r="L26" t="n">
+        <v>95</v>
+      </c>
+      <c r="M26" t="n">
+        <v>74</v>
+      </c>
+      <c r="N26" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 02:23:11.293155</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K27" t="n">
+        <v>75</v>
+      </c>
+      <c r="L27" t="n">
+        <v>96</v>
+      </c>
+      <c r="M27" t="n">
+        <v>76</v>
+      </c>
+      <c r="N27" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 03:12:08.756859</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K28" t="n">
+        <v>76</v>
+      </c>
+      <c r="L28" t="n">
+        <v>95</v>
+      </c>
+      <c r="M28" t="n">
+        <v>75</v>
+      </c>
+      <c r="N28" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 04:22:55.149919</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K29" t="n">
+        <v>75</v>
+      </c>
+      <c r="L29" t="n">
+        <v>96</v>
+      </c>
+      <c r="M29" t="n">
+        <v>76</v>
+      </c>
+      <c r="N29" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 05:06:19.695722</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K30" t="n">
+        <v>78</v>
+      </c>
+      <c r="L30" t="n">
+        <v>93</v>
+      </c>
+      <c r="M30" t="n">
+        <v>78</v>
+      </c>
+      <c r="N30" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 05:31:12.430920</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K31" t="n">
+        <v>80</v>
+      </c>
+      <c r="L31" t="n">
+        <v>91</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85</v>
+      </c>
+      <c r="N31" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K32" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="L32" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="M32" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="N32" t="n">
+        <v>371.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.181</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.181</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.821</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.821</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>balanced_accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>matthews</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tnr</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 07:44:35.868239</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K2" t="n">
+        <v>32</v>
+      </c>
+      <c r="L2" t="n">
+        <v>139</v>
+      </c>
+      <c r="M2" t="n">
+        <v>75</v>
+      </c>
+      <c r="N2" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:08:15.888227</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>167</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:31:46.968463</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>164</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 08:48:38.803271</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="K5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L5" t="n">
+        <v>155</v>
+      </c>
+      <c r="M5" t="n">
+        <v>44</v>
+      </c>
+      <c r="N5" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 09:59:36.444055</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="K6" t="n">
+        <v>22</v>
+      </c>
+      <c r="L6" t="n">
+        <v>149</v>
+      </c>
+      <c r="M6" t="n">
+        <v>49</v>
+      </c>
+      <c r="N6" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 10:29:05.050771</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>171</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 10:55:14.122679</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="K8" t="n">
+        <v>16</v>
+      </c>
+      <c r="L8" t="n">
+        <v>155</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24</v>
+      </c>
+      <c r="N8" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 11:34:23.542862</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>163</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16</v>
+      </c>
+      <c r="N9" t="n">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 12:06:43.200045</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K10" t="n">
+        <v>34</v>
+      </c>
+      <c r="L10" t="n">
+        <v>137</v>
+      </c>
+      <c r="M10" t="n">
+        <v>79</v>
+      </c>
+      <c r="N10" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 12:35:25.531310</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K11" t="n">
+        <v>36</v>
+      </c>
+      <c r="L11" t="n">
+        <v>135</v>
+      </c>
+      <c r="M11" t="n">
+        <v>76</v>
+      </c>
+      <c r="N11" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 13:11:05.045341</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>166</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 13:40:11.319989</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>167</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 14:26:02.720244</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K14" t="n">
+        <v>37</v>
+      </c>
+      <c r="L14" t="n">
+        <v>134</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85</v>
+      </c>
+      <c r="N14" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 15:35:23.127910</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K15" t="n">
+        <v>32</v>
+      </c>
+      <c r="L15" t="n">
+        <v>139</v>
+      </c>
+      <c r="M15" t="n">
+        <v>67</v>
+      </c>
+      <c r="N15" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 16:24:10.880024</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>165</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13</v>
+      </c>
+      <c r="N16" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 17:06:37.273930</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="K17" t="n">
+        <v>31</v>
+      </c>
+      <c r="L17" t="n">
+        <v>140</v>
+      </c>
+      <c r="M17" t="n">
+        <v>71</v>
+      </c>
+      <c r="N17" t="n">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 18:22:09.060886</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>168</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 18:50:48.524789</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="K19" t="n">
+        <v>14</v>
+      </c>
+      <c r="L19" t="n">
+        <v>157</v>
+      </c>
+      <c r="M19" t="n">
+        <v>35</v>
+      </c>
+      <c r="N19" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 19:30:33.229860</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>165</v>
+      </c>
+      <c r="M20" t="n">
+        <v>13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 20:32:46.246451</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="K21" t="n">
+        <v>17</v>
+      </c>
+      <c r="L21" t="n">
+        <v>154</v>
+      </c>
+      <c r="M21" t="n">
+        <v>62</v>
+      </c>
+      <c r="N21" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 21:42:09.219002</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K22" t="n">
+        <v>38</v>
+      </c>
+      <c r="L22" t="n">
+        <v>133</v>
+      </c>
+      <c r="M22" t="n">
+        <v>74</v>
+      </c>
+      <c r="N22" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 22:46:14.791499</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K23" t="n">
+        <v>29</v>
+      </c>
+      <c r="L23" t="n">
+        <v>142</v>
+      </c>
+      <c r="M23" t="n">
+        <v>67</v>
+      </c>
+      <c r="N23" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 23:52:33.342029</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K24" t="n">
+        <v>38</v>
+      </c>
+      <c r="L24" t="n">
+        <v>133</v>
+      </c>
+      <c r="M24" t="n">
+        <v>74</v>
+      </c>
+      <c r="N24" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 01:07:20.126756</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="K25" t="n">
+        <v>29</v>
+      </c>
+      <c r="L25" t="n">
+        <v>142</v>
+      </c>
+      <c r="M25" t="n">
+        <v>60</v>
+      </c>
+      <c r="N25" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 01:44:26.049608</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K26" t="n">
+        <v>16</v>
+      </c>
+      <c r="L26" t="n">
+        <v>155</v>
+      </c>
+      <c r="M26" t="n">
+        <v>56</v>
+      </c>
+      <c r="N26" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 02:23:11.293155</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K27" t="n">
+        <v>38</v>
+      </c>
+      <c r="L27" t="n">
+        <v>133</v>
+      </c>
+      <c r="M27" t="n">
+        <v>76</v>
+      </c>
+      <c r="N27" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 03:12:08.756859</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="K28" t="n">
+        <v>13</v>
+      </c>
+      <c r="L28" t="n">
+        <v>158</v>
+      </c>
+      <c r="M28" t="n">
+        <v>42</v>
+      </c>
+      <c r="N28" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 04:22:55.149919</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="K29" t="n">
+        <v>38</v>
+      </c>
+      <c r="L29" t="n">
+        <v>133</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84</v>
+      </c>
+      <c r="N29" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 05:06:19.695722</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>167</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-22 05:31:12.430920</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="K31" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>163</v>
+      </c>
+      <c r="M31" t="n">
+        <v>15</v>
+      </c>
+      <c r="N31" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="K32" t="n">
+        <v>19.367</v>
+      </c>
+      <c r="L32" t="n">
+        <v>151.633</v>
+      </c>
+      <c r="M32" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>404.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K33" t="n">
+        <v>13.258</v>
+      </c>
+      <c r="L33" t="n">
+        <v>13.258</v>
+      </c>
+      <c r="M33" t="n">
+        <v>29.346</v>
+      </c>
+      <c r="N33" t="n">
+        <v>29.346</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>balanced_accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>matthews</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tnr</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>exp_2026-03-21 07:44:35.868239</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.634</v>
       </c>
       <c r="C2" t="n">
